--- a/backend/data/financials_by_company/1862.HK.xlsx
+++ b/backend/data/financials_by_company/1862.HK.xlsx
@@ -657,570 +657,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-20570197.270621</v>
+        <v>80158500</v>
       </c>
       <c r="C2" t="n">
-        <v>0.026683</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-1858153000</v>
+        <v>1578782000</v>
       </c>
       <c r="E2" t="n">
-        <v>-739859000</v>
+        <v>320634000</v>
       </c>
       <c r="F2" t="n">
-        <v>-770907000</v>
+        <v>320634000</v>
       </c>
       <c r="G2" t="n">
-        <v>-3003782000</v>
+        <v>127543000</v>
       </c>
       <c r="H2" t="n">
-        <v>12754000</v>
+        <v>-16327000</v>
       </c>
       <c r="I2" t="n">
-        <v>6158911000</v>
+        <v>11111689000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2598012000</v>
+        <v>1899416000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2610766000</v>
+        <v>1899416000</v>
       </c>
       <c r="L2" t="n">
-        <v>-722097000</v>
+        <v>-523213000</v>
       </c>
       <c r="M2" t="n">
-        <v>723253000</v>
+        <v>859158000</v>
       </c>
       <c r="N2" t="n">
-        <v>1156000</v>
+        <v>335945000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2222397197.270621</v>
+        <v>-112932500</v>
       </c>
       <c r="P2" t="n">
-        <v>-3003782000</v>
+        <v>127543000</v>
       </c>
       <c r="Q2" t="n">
-        <v>7167843000</v>
+        <v>12325666000</v>
       </c>
       <c r="R2" t="n">
-        <v>-2417601000</v>
+        <v>1464441000</v>
       </c>
       <c r="S2" t="n">
-        <v>1538813000</v>
+        <v>1536816000</v>
       </c>
       <c r="T2" t="n">
-        <v>1538813000</v>
+        <v>1536319000</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.95</v>
+        <v>0.08</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.95</v>
+        <v>0.08</v>
       </c>
       <c r="W2" t="n">
-        <v>-3003782000</v>
+        <v>127543000</v>
       </c>
       <c r="X2" t="n">
-        <v>-3003782000</v>
+        <v>127543000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3003782000</v>
+        <v>127543000</v>
       </c>
       <c r="AA2" t="n">
-        <v>241275000</v>
+        <v>-266270000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3245057000</v>
+        <v>393813000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3245057000</v>
+        <v>393813000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-88962000</v>
+        <v>646445000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3334019000</v>
+        <v>1040258000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-19228000</v>
+        <v>-104468000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-223813000</v>
+        <v>157955000</v>
       </c>
       <c r="AH2" t="n">
-        <v>42014000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>150751000</v>
-      </c>
+        <v>-157955000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-722097000</v>
+        <v>-523213000</v>
       </c>
       <c r="AK2" t="n">
-        <v>723253000</v>
+        <v>859158000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1156000</v>
+        <v>335945000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1261443000</v>
+        <v>1225978000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1008932000</v>
+        <v>1213977000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1017164000</v>
+        <v>1231209000</v>
       </c>
       <c r="AP2" t="n">
-        <v>350191000</v>
+        <v>580343000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>666973000</v>
+        <v>650866000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-252511000</v>
+        <v>2439955000</v>
       </c>
       <c r="AS2" t="n">
-        <v>6158911000</v>
+        <v>11111689000</v>
       </c>
       <c r="AT2" t="n">
-        <v>5906400000</v>
+        <v>13551644000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5906400000</v>
+        <v>13551644000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-111412750</v>
+        <v>-177131500</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-531709000</v>
+        <v>-2107071000</v>
       </c>
       <c r="E3" t="n">
-        <v>-411893000</v>
+        <v>-708526000</v>
       </c>
       <c r="F3" t="n">
-        <v>-445651000</v>
+        <v>-708526000</v>
       </c>
       <c r="G3" t="n">
-        <v>-1721220000</v>
+        <v>-4269792000</v>
       </c>
       <c r="H3" t="n">
-        <v>21174000</v>
+        <v>30385000</v>
       </c>
       <c r="I3" t="n">
-        <v>6830159000</v>
+        <v>7792740000</v>
       </c>
       <c r="J3" t="n">
-        <v>-943602000</v>
+        <v>-2815597000</v>
       </c>
       <c r="K3" t="n">
-        <v>-964776000</v>
+        <v>-2845982000</v>
       </c>
       <c r="L3" t="n">
-        <v>-733684000</v>
+        <v>-946169000</v>
       </c>
       <c r="M3" t="n">
-        <v>750736000</v>
+        <v>1245459000</v>
       </c>
       <c r="N3" t="n">
-        <v>17052000</v>
+        <v>299290000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1353223750</v>
+        <v>-3738397500</v>
       </c>
       <c r="P3" t="n">
-        <v>-1721220000</v>
+        <v>-4269792000</v>
       </c>
       <c r="Q3" t="n">
-        <v>7445928000</v>
+        <v>9260312000</v>
       </c>
       <c r="R3" t="n">
-        <v>-711720000</v>
+        <v>-2146061000</v>
       </c>
       <c r="S3" t="n">
-        <v>1537204000</v>
+        <v>1536908000</v>
       </c>
       <c r="T3" t="n">
-        <v>1537204000</v>
+        <v>1536908000</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.12</v>
+        <v>-2.78</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.12</v>
+        <v>-2.78</v>
       </c>
       <c r="W3" t="n">
-        <v>-1721220000</v>
+        <v>-4269792000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1721220000</v>
+        <v>-4269792000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1721220000</v>
+        <v>-4269792000</v>
       </c>
       <c r="AA3" t="n">
-        <v>120111000</v>
+        <v>8088000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1841331000</v>
+        <v>-4277880000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1841331000</v>
+        <v>-4277880000</v>
       </c>
       <c r="AD3" t="n">
-        <v>125819000</v>
+        <v>186439000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1715512000</v>
+        <v>-4091441000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-33785000</v>
+        <v>-15086000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-68165000</v>
+        <v>-328254000</v>
       </c>
       <c r="AH3" t="n">
-        <v>34407000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
+        <v>328254000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-733684000</v>
+        <v>-946169000</v>
       </c>
       <c r="AK3" t="n">
-        <v>750736000</v>
+        <v>1245459000</v>
       </c>
       <c r="AL3" t="n">
-        <v>17052000</v>
+        <v>299290000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-151453000</v>
+        <v>-1352406000</v>
       </c>
       <c r="AN3" t="n">
-        <v>615769000</v>
+        <v>1467572000</v>
       </c>
       <c r="AO3" t="n">
-        <v>631818000</v>
+        <v>1482966000</v>
       </c>
       <c r="AP3" t="n">
-        <v>320980000</v>
+        <v>560455000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>310838000</v>
+        <v>922511000</v>
       </c>
       <c r="AR3" t="n">
-        <v>464316000</v>
+        <v>115166000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6830159000</v>
+        <v>7792740000</v>
       </c>
       <c r="AT3" t="n">
-        <v>7294475000</v>
+        <v>7907906000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7294475000</v>
+        <v>7907906000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-177131500</v>
+        <v>-111412750</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-2107071000</v>
+        <v>-531709000</v>
       </c>
       <c r="E4" t="n">
-        <v>-708526000</v>
+        <v>-411893000</v>
       </c>
       <c r="F4" t="n">
-        <v>-708526000</v>
+        <v>-445651000</v>
       </c>
       <c r="G4" t="n">
-        <v>-4269792000</v>
+        <v>-1721220000</v>
       </c>
       <c r="H4" t="n">
-        <v>30385000</v>
+        <v>21174000</v>
       </c>
       <c r="I4" t="n">
-        <v>7792740000</v>
+        <v>6830159000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2815597000</v>
+        <v>-943602000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2845982000</v>
+        <v>-964776000</v>
       </c>
       <c r="L4" t="n">
-        <v>-946169000</v>
+        <v>-733684000</v>
       </c>
       <c r="M4" t="n">
-        <v>1245459000</v>
+        <v>750736000</v>
       </c>
       <c r="N4" t="n">
-        <v>299290000</v>
+        <v>17052000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3738397500</v>
+        <v>-1353223750</v>
       </c>
       <c r="P4" t="n">
-        <v>-4269792000</v>
+        <v>-1721220000</v>
       </c>
       <c r="Q4" t="n">
-        <v>9260312000</v>
+        <v>7445928000</v>
       </c>
       <c r="R4" t="n">
-        <v>-2146061000</v>
+        <v>-711720000</v>
       </c>
       <c r="S4" t="n">
-        <v>1536908000</v>
+        <v>1537204000</v>
       </c>
       <c r="T4" t="n">
-        <v>1536908000</v>
+        <v>1537204000</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.78</v>
+        <v>-1.12</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.78</v>
+        <v>-1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>-4269792000</v>
+        <v>-1721220000</v>
       </c>
       <c r="X4" t="n">
-        <v>-4269792000</v>
+        <v>-1721220000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-4269792000</v>
+        <v>-1721220000</v>
       </c>
       <c r="AA4" t="n">
-        <v>8088000</v>
+        <v>120111000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4277880000</v>
+        <v>-1841331000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4277880000</v>
+        <v>-1841331000</v>
       </c>
       <c r="AD4" t="n">
-        <v>186439000</v>
+        <v>125819000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-4091441000</v>
+        <v>-1715512000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-15086000</v>
+        <v>-33785000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-328254000</v>
+        <v>-68165000</v>
       </c>
       <c r="AH4" t="n">
-        <v>328254000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>34407000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-946169000</v>
+        <v>-733684000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1245459000</v>
+        <v>750736000</v>
       </c>
       <c r="AL4" t="n">
-        <v>299290000</v>
+        <v>17052000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1352406000</v>
+        <v>-151453000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1467572000</v>
+        <v>615769000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1482966000</v>
+        <v>631818000</v>
       </c>
       <c r="AP4" t="n">
-        <v>560455000</v>
+        <v>320980000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>922511000</v>
+        <v>310838000</v>
       </c>
       <c r="AR4" t="n">
-        <v>115166000</v>
+        <v>464316000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7792740000</v>
+        <v>6830159000</v>
       </c>
       <c r="AT4" t="n">
-        <v>7907906000</v>
+        <v>7294475000</v>
       </c>
       <c r="AU4" t="n">
-        <v>7907906000</v>
+        <v>7294475000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>80158500</v>
+        <v>-20570197.270621</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.026683</v>
       </c>
       <c r="D5" t="n">
-        <v>1578782000</v>
+        <v>-1858153000</v>
       </c>
       <c r="E5" t="n">
-        <v>320634000</v>
+        <v>-739859000</v>
       </c>
       <c r="F5" t="n">
-        <v>320634000</v>
+        <v>-770907000</v>
       </c>
       <c r="G5" t="n">
-        <v>127543000</v>
+        <v>-3003782000</v>
       </c>
       <c r="H5" t="n">
-        <v>-16327000</v>
+        <v>12754000</v>
       </c>
       <c r="I5" t="n">
-        <v>11111689000</v>
+        <v>6158911000</v>
       </c>
       <c r="J5" t="n">
-        <v>1899416000</v>
+        <v>-2598012000</v>
       </c>
       <c r="K5" t="n">
-        <v>1899416000</v>
+        <v>-2610766000</v>
       </c>
       <c r="L5" t="n">
-        <v>-523213000</v>
+        <v>-722097000</v>
       </c>
       <c r="M5" t="n">
-        <v>859158000</v>
+        <v>723253000</v>
       </c>
       <c r="N5" t="n">
-        <v>335945000</v>
+        <v>1156000</v>
       </c>
       <c r="O5" t="n">
-        <v>-112932500</v>
+        <v>-2222397197.270621</v>
       </c>
       <c r="P5" t="n">
-        <v>127543000</v>
+        <v>-3003782000</v>
       </c>
       <c r="Q5" t="n">
-        <v>12325666000</v>
+        <v>7167843000</v>
       </c>
       <c r="R5" t="n">
-        <v>1464441000</v>
+        <v>-2417601000</v>
       </c>
       <c r="S5" t="n">
-        <v>1536816000</v>
+        <v>1538813000</v>
       </c>
       <c r="T5" t="n">
-        <v>1536319000</v>
+        <v>1538813000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08</v>
+        <v>-1.95</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08</v>
+        <v>-1.95</v>
       </c>
       <c r="W5" t="n">
-        <v>127543000</v>
+        <v>-3003782000</v>
       </c>
       <c r="X5" t="n">
-        <v>127543000</v>
+        <v>-3003782000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>127543000</v>
+        <v>-3003782000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-266270000</v>
+        <v>241275000</v>
       </c>
       <c r="AB5" t="n">
-        <v>393813000</v>
+        <v>-3245057000</v>
       </c>
       <c r="AC5" t="n">
-        <v>393813000</v>
+        <v>-3245057000</v>
       </c>
       <c r="AD5" t="n">
-        <v>646445000</v>
+        <v>-88962000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1040258000</v>
+        <v>-3334019000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-104468000</v>
+        <v>-19228000</v>
       </c>
       <c r="AG5" t="n">
-        <v>157955000</v>
+        <v>-223813000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-157955000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>42014000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>150751000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-523213000</v>
+        <v>-722097000</v>
       </c>
       <c r="AK5" t="n">
-        <v>859158000</v>
+        <v>723253000</v>
       </c>
       <c r="AL5" t="n">
-        <v>335945000</v>
+        <v>1156000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1225978000</v>
+        <v>-1261443000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1213977000</v>
+        <v>1008932000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1231209000</v>
+        <v>1017164000</v>
       </c>
       <c r="AP5" t="n">
-        <v>580343000</v>
+        <v>350191000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>650866000</v>
+        <v>666973000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2439955000</v>
+        <v>-252511000</v>
       </c>
       <c r="AS5" t="n">
-        <v>11111689000</v>
+        <v>6158911000</v>
       </c>
       <c r="AT5" t="n">
-        <v>13551644000</v>
+        <v>5906400000</v>
       </c>
       <c r="AU5" t="n">
-        <v>13551644000</v>
+        <v>5906400000</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1538813213</v>
@@ -1610,49 +1610,47 @@
         <v>1538813213</v>
       </c>
       <c r="D2" t="n">
-        <v>15615923000</v>
+        <v>19386595000</v>
       </c>
       <c r="E2" t="n">
-        <v>15947440000</v>
+        <v>21743174000</v>
       </c>
       <c r="F2" t="n">
-        <v>-3040803000</v>
+        <v>5863587000</v>
       </c>
       <c r="G2" t="n">
-        <v>13075051000</v>
+        <v>27636528000</v>
       </c>
       <c r="H2" t="n">
-        <v>-3770987000</v>
+        <v>13140792000</v>
       </c>
       <c r="I2" t="n">
-        <v>-3040803000</v>
+        <v>5863587000</v>
       </c>
       <c r="J2" t="n">
-        <v>5177000</v>
+        <v>145137000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2867212000</v>
+        <v>6038491000</v>
       </c>
       <c r="L2" t="n">
-        <v>-130956000</v>
+        <v>16708189000</v>
       </c>
       <c r="M2" t="n">
-        <v>684739000</v>
+        <v>11236992000</v>
       </c>
       <c r="N2" t="n">
-        <v>3551951000</v>
+        <v>5198501000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2867212000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>87174000</v>
-      </c>
+        <v>6038491000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6215000</v>
       </c>
       <c r="R2" t="n">
-        <v>-4266143000</v>
+        <v>4728651000</v>
       </c>
       <c r="S2" t="n">
         <v>424007000</v>
@@ -1664,151 +1662,163 @@
         <v>87813000</v>
       </c>
       <c r="V2" t="n">
-        <v>29933034000</v>
+        <v>52012751000</v>
       </c>
       <c r="W2" t="n">
-        <v>3504629000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>13001227000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1034876000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>768288000</v>
+        <v>1171872000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2736341000</v>
+        <v>10794479000</v>
       </c>
       <c r="AA2" t="n">
-        <v>85000</v>
+        <v>124781000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2736256000</v>
+        <v>10669698000</v>
       </c>
       <c r="AC2" t="n">
-        <v>26428405000</v>
+        <v>39011524000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13211099000</v>
+        <v>10948695000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5092000</v>
+        <v>20356000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13206007000</v>
+        <v>10928339000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10333705000</v>
+        <v>16890043000</v>
       </c>
       <c r="AH2" t="n">
-        <v>5835260000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>223582000</v>
-      </c>
+        <v>1498982000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>2401443000</v>
+        <v>2127122000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1873420000</v>
+        <v>13263939000</v>
       </c>
       <c r="AL2" t="n">
-        <v>30617773000</v>
+        <v>63249743000</v>
       </c>
       <c r="AM2" t="n">
-        <v>7960355000</v>
+        <v>11097427000</v>
       </c>
       <c r="AN2" t="n">
-        <v>444160000</v>
+        <v>429344000</v>
       </c>
       <c r="AO2" t="n">
-        <v>998050000</v>
+        <v>1507964000</v>
       </c>
       <c r="AP2" t="n">
-        <v>429000000</v>
+        <v>456703000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>569050000</v>
+        <v>1051261000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1364804000</v>
+        <v>2342526000</v>
       </c>
       <c r="AS2" t="n">
-        <v>839861000</v>
+        <v>1343964000</v>
       </c>
       <c r="AT2" t="n">
-        <v>524943000</v>
+        <v>998562000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4193600000</v>
+        <v>5893100000</v>
       </c>
       <c r="AV2" t="n">
-        <v>173591000</v>
+        <v>174904000</v>
       </c>
       <c r="AW2" t="n">
-        <v>119245000</v>
+        <v>132477000</v>
       </c>
       <c r="AX2" t="n">
-        <v>54346000</v>
+        <v>42427000</v>
       </c>
       <c r="AY2" t="n">
-        <v>69567000</v>
+        <v>94285000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-136809000</v>
+        <v>-98687000</v>
       </c>
       <c r="BA2" t="n">
-        <v>206376000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>192972000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>221307000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>65010000</v>
+        <v>61628000</v>
       </c>
       <c r="BD2" t="n">
-        <v>141366000</v>
+        <v>131344000</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>22657418000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+        <v>52152316000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>54304000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>105000000</v>
+      </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>8779513000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>422917000</v>
+        <v>508018000</v>
       </c>
       <c r="BK2" t="n">
-        <v>14342629000</v>
+        <v>29563157000</v>
       </c>
       <c r="BL2" t="n">
-        <v>14342629000</v>
+        <v>29563157000</v>
       </c>
       <c r="BM2" t="n">
-        <v>101457000</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>253107000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>453714000</v>
+      </c>
       <c r="BO2" t="n">
-        <v>6947509000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
+        <v>9743610000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-38137000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>501722000</v>
+      </c>
       <c r="BR2" t="n">
-        <v>842906000</v>
+        <v>3199911000</v>
       </c>
       <c r="BS2" t="n">
-        <v>516566000</v>
+        <v>988469000</v>
       </c>
       <c r="BT2" t="n">
-        <v>326340000</v>
+        <v>2211442000</v>
       </c>
       <c r="BU2" t="n">
-        <v>326340000</v>
+        <v>2211442000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1538813213</v>
@@ -1817,49 +1827,49 @@
         <v>1538813213</v>
       </c>
       <c r="D3" t="n">
-        <v>16249871000</v>
+        <v>17060601000</v>
       </c>
       <c r="E3" t="n">
-        <v>16901988000</v>
+        <v>18538287000</v>
       </c>
       <c r="F3" t="n">
-        <v>-54777000</v>
+        <v>1548547000</v>
       </c>
       <c r="G3" t="n">
-        <v>17028730000</v>
+        <v>20206361000</v>
       </c>
       <c r="H3" t="n">
-        <v>752407000</v>
+        <v>2474348000</v>
       </c>
       <c r="I3" t="n">
-        <v>-54777000</v>
+        <v>1548547000</v>
       </c>
       <c r="J3" t="n">
-        <v>25866000</v>
+        <v>125598000</v>
       </c>
       <c r="K3" t="n">
-        <v>152608000</v>
+        <v>1793672000</v>
       </c>
       <c r="L3" t="n">
-        <v>4724287000</v>
+        <v>6909648000</v>
       </c>
       <c r="M3" t="n">
-        <v>4204823000</v>
+        <v>6398697000</v>
       </c>
       <c r="N3" t="n">
-        <v>4052215000</v>
+        <v>4605025000</v>
       </c>
       <c r="O3" t="n">
-        <v>152608000</v>
+        <v>1793672000</v>
       </c>
       <c r="P3" t="n">
-        <v>87174000</v>
+        <v>91507000</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4333000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1262361000</v>
+        <v>458859000</v>
       </c>
       <c r="S3" t="n">
         <v>424007000</v>
@@ -1871,153 +1881,155 @@
         <v>87813000</v>
       </c>
       <c r="V3" t="n">
-        <v>35302737000</v>
+        <v>40711147000</v>
       </c>
       <c r="W3" t="n">
-        <v>5597115000</v>
+        <v>6280466000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>1012013000</v>
+        <v>1062151000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4585102000</v>
+        <v>5218315000</v>
       </c>
       <c r="AA3" t="n">
-        <v>13423000</v>
+        <v>102339000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4571679000</v>
+        <v>5115976000</v>
       </c>
       <c r="AC3" t="n">
-        <v>29705622000</v>
+        <v>34430681000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12316886000</v>
+        <v>13319972000</v>
       </c>
       <c r="AE3" t="n">
-        <v>12443000</v>
+        <v>23259000</v>
       </c>
       <c r="AF3" t="n">
-        <v>12304443000</v>
+        <v>13296713000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11264303000</v>
+        <v>12420862000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5891335000</v>
+        <v>6317836000</v>
       </c>
       <c r="AI3" t="n">
         <v>223582000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2776983000</v>
+        <v>3243396000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2372403000</v>
+        <v>2636048000</v>
       </c>
       <c r="AL3" t="n">
-        <v>39507560000</v>
+        <v>47109844000</v>
       </c>
       <c r="AM3" t="n">
-        <v>9049531000</v>
+        <v>10204815000</v>
       </c>
       <c r="AN3" t="n">
-        <v>519030000</v>
+        <v>603600000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1128922000</v>
+        <v>1348031000</v>
       </c>
       <c r="AP3" t="n">
-        <v>442788000</v>
+        <v>492527000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>686134000</v>
+        <v>855504000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1763308000</v>
+        <v>2067611000</v>
       </c>
       <c r="AS3" t="n">
-        <v>943240000</v>
+        <v>1243221000</v>
       </c>
       <c r="AT3" t="n">
-        <v>820068000</v>
+        <v>824390000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4646900000</v>
+        <v>5146100000</v>
       </c>
       <c r="AV3" t="n">
-        <v>207385000</v>
+        <v>245125000</v>
       </c>
       <c r="AW3" t="n">
-        <v>121991000</v>
+        <v>125973000</v>
       </c>
       <c r="AX3" t="n">
-        <v>85394000</v>
+        <v>119152000</v>
       </c>
       <c r="AY3" t="n">
-        <v>80129000</v>
+        <v>79647000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-148334000</v>
+        <v>-135869000</v>
       </c>
       <c r="BA3" t="n">
-        <v>228463000</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>215516000</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>204077000</v>
+      </c>
       <c r="BC3" t="n">
-        <v>71794000</v>
+        <v>71495000</v>
       </c>
       <c r="BD3" t="n">
-        <v>156669000</v>
+        <v>144021000</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>30458029000</v>
+        <v>36905029000</v>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>128000000</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>449088000</v>
+        <v>542657000</v>
       </c>
       <c r="BK3" t="n">
-        <v>20979614000</v>
+        <v>25793013000</v>
       </c>
       <c r="BL3" t="n">
-        <v>20979614000</v>
+        <v>25793013000</v>
       </c>
       <c r="BM3" t="n">
-        <v>269531000</v>
+        <v>277868000</v>
       </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
-        <v>7506588000</v>
+        <v>8025028000</v>
       </c>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="n">
-        <v>1253208000</v>
+        <v>2138463000</v>
       </c>
       <c r="BS3" t="n">
-        <v>626957000</v>
+        <v>786375000</v>
       </c>
       <c r="BT3" t="n">
-        <v>626251000</v>
+        <v>1352088000</v>
       </c>
       <c r="BU3" t="n">
-        <v>626251000</v>
+        <v>1352088000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1538813213</v>
@@ -2026,49 +2038,49 @@
         <v>1538813213</v>
       </c>
       <c r="D4" t="n">
-        <v>17060601000</v>
+        <v>16249871000</v>
       </c>
       <c r="E4" t="n">
-        <v>18538287000</v>
+        <v>16901988000</v>
       </c>
       <c r="F4" t="n">
-        <v>1548547000</v>
+        <v>-54777000</v>
       </c>
       <c r="G4" t="n">
-        <v>20206361000</v>
+        <v>17028730000</v>
       </c>
       <c r="H4" t="n">
-        <v>2474348000</v>
+        <v>752407000</v>
       </c>
       <c r="I4" t="n">
-        <v>1548547000</v>
+        <v>-54777000</v>
       </c>
       <c r="J4" t="n">
-        <v>125598000</v>
+        <v>25866000</v>
       </c>
       <c r="K4" t="n">
-        <v>1793672000</v>
+        <v>152608000</v>
       </c>
       <c r="L4" t="n">
-        <v>6909648000</v>
+        <v>4724287000</v>
       </c>
       <c r="M4" t="n">
-        <v>6398697000</v>
+        <v>4204823000</v>
       </c>
       <c r="N4" t="n">
-        <v>4605025000</v>
+        <v>4052215000</v>
       </c>
       <c r="O4" t="n">
-        <v>1793672000</v>
+        <v>152608000</v>
       </c>
       <c r="P4" t="n">
-        <v>91507000</v>
+        <v>87174000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4333000</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>458859000</v>
+        <v>-1262361000</v>
       </c>
       <c r="S4" t="n">
         <v>424007000</v>
@@ -2080,155 +2092,153 @@
         <v>87813000</v>
       </c>
       <c r="V4" t="n">
-        <v>40711147000</v>
+        <v>35302737000</v>
       </c>
       <c r="W4" t="n">
-        <v>6280466000</v>
+        <v>5597115000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>1062151000</v>
+        <v>1012013000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5218315000</v>
+        <v>4585102000</v>
       </c>
       <c r="AA4" t="n">
-        <v>102339000</v>
+        <v>13423000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5115976000</v>
+        <v>4571679000</v>
       </c>
       <c r="AC4" t="n">
-        <v>34430681000</v>
+        <v>29705622000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13319972000</v>
+        <v>12316886000</v>
       </c>
       <c r="AE4" t="n">
-        <v>23259000</v>
+        <v>12443000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13296713000</v>
+        <v>12304443000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12420862000</v>
+        <v>11264303000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6317836000</v>
+        <v>5891335000</v>
       </c>
       <c r="AI4" t="n">
         <v>223582000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3243396000</v>
+        <v>2776983000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2636048000</v>
+        <v>2372403000</v>
       </c>
       <c r="AL4" t="n">
-        <v>47109844000</v>
+        <v>39507560000</v>
       </c>
       <c r="AM4" t="n">
-        <v>10204815000</v>
+        <v>9049531000</v>
       </c>
       <c r="AN4" t="n">
-        <v>603600000</v>
+        <v>519030000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1348031000</v>
+        <v>1128922000</v>
       </c>
       <c r="AP4" t="n">
-        <v>492527000</v>
+        <v>442788000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>855504000</v>
+        <v>686134000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2067611000</v>
+        <v>1763308000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1243221000</v>
+        <v>943240000</v>
       </c>
       <c r="AT4" t="n">
-        <v>824390000</v>
+        <v>820068000</v>
       </c>
       <c r="AU4" t="n">
-        <v>5146100000</v>
+        <v>4646900000</v>
       </c>
       <c r="AV4" t="n">
-        <v>245125000</v>
+        <v>207385000</v>
       </c>
       <c r="AW4" t="n">
-        <v>125973000</v>
+        <v>121991000</v>
       </c>
       <c r="AX4" t="n">
-        <v>119152000</v>
+        <v>85394000</v>
       </c>
       <c r="AY4" t="n">
-        <v>79647000</v>
+        <v>80129000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-135869000</v>
+        <v>-148334000</v>
       </c>
       <c r="BA4" t="n">
-        <v>215516000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>204077000</v>
-      </c>
+        <v>228463000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>71495000</v>
+        <v>71794000</v>
       </c>
       <c r="BD4" t="n">
-        <v>144021000</v>
+        <v>156669000</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>36905029000</v>
+        <v>30458029000</v>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>128000000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>542657000</v>
+        <v>449088000</v>
       </c>
       <c r="BK4" t="n">
-        <v>25793013000</v>
+        <v>20979614000</v>
       </c>
       <c r="BL4" t="n">
-        <v>25793013000</v>
+        <v>20979614000</v>
       </c>
       <c r="BM4" t="n">
-        <v>277868000</v>
+        <v>269531000</v>
       </c>
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>8025028000</v>
+        <v>7506588000</v>
       </c>
       <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
-        <v>2138463000</v>
+        <v>1253208000</v>
       </c>
       <c r="BS4" t="n">
-        <v>786375000</v>
+        <v>626957000</v>
       </c>
       <c r="BT4" t="n">
-        <v>1352088000</v>
+        <v>626251000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1352088000</v>
+        <v>626251000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1538813213</v>
@@ -2237,47 +2247,49 @@
         <v>1538813213</v>
       </c>
       <c r="D5" t="n">
-        <v>19386595000</v>
+        <v>15615923000</v>
       </c>
       <c r="E5" t="n">
-        <v>21743174000</v>
+        <v>15947440000</v>
       </c>
       <c r="F5" t="n">
-        <v>5863587000</v>
+        <v>-3040803000</v>
       </c>
       <c r="G5" t="n">
-        <v>27636528000</v>
+        <v>13075051000</v>
       </c>
       <c r="H5" t="n">
-        <v>13140792000</v>
+        <v>-3770987000</v>
       </c>
       <c r="I5" t="n">
-        <v>5863587000</v>
+        <v>-3040803000</v>
       </c>
       <c r="J5" t="n">
-        <v>145137000</v>
+        <v>5177000</v>
       </c>
       <c r="K5" t="n">
-        <v>6038491000</v>
+        <v>-2867212000</v>
       </c>
       <c r="L5" t="n">
-        <v>16708189000</v>
+        <v>-130956000</v>
       </c>
       <c r="M5" t="n">
-        <v>11236992000</v>
+        <v>684739000</v>
       </c>
       <c r="N5" t="n">
-        <v>5198501000</v>
+        <v>3551951000</v>
       </c>
       <c r="O5" t="n">
-        <v>6038491000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>-2867212000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>87174000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>6215000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4728651000</v>
+        <v>-4266143000</v>
       </c>
       <c r="S5" t="n">
         <v>424007000</v>
@@ -2289,158 +2301,146 @@
         <v>87813000</v>
       </c>
       <c r="V5" t="n">
-        <v>52012751000</v>
+        <v>29933034000</v>
       </c>
       <c r="W5" t="n">
-        <v>13001227000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1034876000</v>
-      </c>
+        <v>3504629000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>1171872000</v>
+        <v>768288000</v>
       </c>
       <c r="Z5" t="n">
-        <v>10794479000</v>
+        <v>2736341000</v>
       </c>
       <c r="AA5" t="n">
-        <v>124781000</v>
+        <v>85000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10669698000</v>
+        <v>2736256000</v>
       </c>
       <c r="AC5" t="n">
-        <v>39011524000</v>
+        <v>26428405000</v>
       </c>
       <c r="AD5" t="n">
-        <v>10948695000</v>
+        <v>13211099000</v>
       </c>
       <c r="AE5" t="n">
-        <v>20356000</v>
+        <v>5092000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10928339000</v>
+        <v>13206007000</v>
       </c>
       <c r="AG5" t="n">
-        <v>16890043000</v>
+        <v>10333705000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1498982000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>5835260000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>223582000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>2127122000</v>
+        <v>2401443000</v>
       </c>
       <c r="AK5" t="n">
-        <v>13263939000</v>
+        <v>1873420000</v>
       </c>
       <c r="AL5" t="n">
-        <v>63249743000</v>
+        <v>30617773000</v>
       </c>
       <c r="AM5" t="n">
-        <v>11097427000</v>
+        <v>7960355000</v>
       </c>
       <c r="AN5" t="n">
-        <v>429344000</v>
+        <v>444160000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1507964000</v>
+        <v>998050000</v>
       </c>
       <c r="AP5" t="n">
-        <v>456703000</v>
+        <v>429000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1051261000</v>
+        <v>569050000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2342526000</v>
+        <v>1364804000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1343964000</v>
+        <v>839861000</v>
       </c>
       <c r="AT5" t="n">
-        <v>998562000</v>
+        <v>524943000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5893100000</v>
+        <v>4193600000</v>
       </c>
       <c r="AV5" t="n">
-        <v>174904000</v>
+        <v>173591000</v>
       </c>
       <c r="AW5" t="n">
-        <v>132477000</v>
+        <v>119245000</v>
       </c>
       <c r="AX5" t="n">
-        <v>42427000</v>
+        <v>54346000</v>
       </c>
       <c r="AY5" t="n">
-        <v>94285000</v>
+        <v>69567000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-98687000</v>
+        <v>-136809000</v>
       </c>
       <c r="BA5" t="n">
-        <v>192972000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>221307000</v>
-      </c>
+        <v>206376000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>61628000</v>
+        <v>65010000</v>
       </c>
       <c r="BD5" t="n">
-        <v>131344000</v>
+        <v>141366000</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>52152316000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>54304000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>105000000</v>
-      </c>
+        <v>22657418000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>8779513000</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>508018000</v>
+        <v>422917000</v>
       </c>
       <c r="BK5" t="n">
-        <v>29563157000</v>
+        <v>14342629000</v>
       </c>
       <c r="BL5" t="n">
-        <v>29563157000</v>
+        <v>14342629000</v>
       </c>
       <c r="BM5" t="n">
-        <v>253107000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>453714000</v>
-      </c>
+        <v>101457000</v>
+      </c>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
-        <v>9743610000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-38137000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>501722000</v>
-      </c>
+        <v>6947509000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
-        <v>3199911000</v>
+        <v>842906000</v>
       </c>
       <c r="BS5" t="n">
-        <v>988469000</v>
+        <v>516566000</v>
       </c>
       <c r="BT5" t="n">
-        <v>2211442000</v>
+        <v>326340000</v>
       </c>
       <c r="BU5" t="n">
-        <v>2211442000</v>
+        <v>326340000</v>
       </c>
     </row>
   </sheetData>
@@ -2746,664 +2746,664 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>38969000</v>
+        <v>-4853416000</v>
       </c>
       <c r="C2" t="n">
-        <v>-371109000</v>
+        <v>-12344638000</v>
       </c>
       <c r="D2" t="n">
-        <v>99990000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>13406105000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-7126000</v>
+        <v>-8748000</v>
       </c>
       <c r="G2" t="n">
-        <v>217757000</v>
+        <v>2211442000</v>
       </c>
       <c r="H2" t="n">
-        <v>334532000</v>
+        <v>10895964000</v>
       </c>
       <c r="I2" t="n">
-        <v>-15000</v>
+        <v>-1385000</v>
       </c>
       <c r="J2" t="n">
-        <v>-116760000</v>
+        <v>-8683137000</v>
       </c>
       <c r="K2" t="n">
-        <v>-288760000</v>
+        <v>-3881587000</v>
       </c>
       <c r="L2" t="n">
-        <v>-13567000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-4569424000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-350867000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-350867000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-271119000</v>
+        <v>1061467000</v>
       </c>
       <c r="R2" t="n">
-        <v>-271119000</v>
+        <v>1061467000</v>
       </c>
       <c r="S2" t="n">
-        <v>-371109000</v>
+        <v>-12344638000</v>
       </c>
       <c r="T2" t="n">
-        <v>99990000</v>
+        <v>13406105000</v>
       </c>
       <c r="U2" t="n">
-        <v>125905000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>43118000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11195000</v>
+      </c>
       <c r="W2" t="n">
-        <v>1156000</v>
+        <v>328416000</v>
       </c>
       <c r="X2" t="n">
-        <v>13903000</v>
+        <v>66280000</v>
       </c>
       <c r="Y2" t="n">
-        <v>36569000</v>
+        <v>-168270000</v>
       </c>
       <c r="Z2" t="n">
-        <v>36569000</v>
+        <v>608736000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-777006000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>36374000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>45266000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-8892000</v>
       </c>
       <c r="AE2" t="n">
-        <v>94012000</v>
+        <v>275443000</v>
       </c>
       <c r="AF2" t="n">
-        <v>94462000</v>
+        <v>340390000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-450000</v>
+        <v>-64947000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-2854000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-2854000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-7116000</v>
+        <v>4122000</v>
       </c>
       <c r="AK2" t="n">
-        <v>10000</v>
+        <v>10016000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-7126000</v>
+        <v>-5894000</v>
       </c>
       <c r="AM2" t="n">
-        <v>46095000</v>
+        <v>-4844668000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-32955000</v>
+        <v>-859109000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-104029000</v>
+        <v>-1640806000</v>
       </c>
       <c r="AP2" t="n">
-        <v>899891000</v>
+        <v>-3580567000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-3057696000</v>
+        <v>-7480018000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1360194000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>733636000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1185476000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>4758809000</v>
+        <v>1127274000</v>
       </c>
       <c r="AU2" t="n">
-        <v>558972000</v>
+        <v>853065000</v>
       </c>
       <c r="AV2" t="n">
-        <v>722097000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
+        <v>524544000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>837000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>71931000</v>
+      </c>
       <c r="AY2" t="n">
-        <v>12754000</v>
+        <v>-16327000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>153000</v>
+        <v>1471000</v>
       </c>
       <c r="BA2" t="n">
-        <v>12601000</v>
+        <v>-17798000</v>
       </c>
       <c r="BB2" t="n">
-        <v>841004000</v>
+        <v>-219291000</v>
       </c>
       <c r="BC2" t="n">
-        <v>149837000</v>
+        <v>-254393000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4951000</v>
+        <v>-310000</v>
       </c>
       <c r="BE2" t="n">
-        <v>100923000</v>
+        <v>-157645000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-3334019000</v>
+        <v>1040258000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1341983000</v>
+        <v>345411000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2310166000</v>
+        <v>-5657270000</v>
       </c>
       <c r="D3" t="n">
-        <v>673642000</v>
+        <v>1890953000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-2549000</v>
+        <v>-13105000</v>
       </c>
       <c r="G3" t="n">
-        <v>334532000</v>
+        <v>670410000</v>
       </c>
       <c r="H3" t="n">
-        <v>670410000</v>
+        <v>2211442000</v>
       </c>
       <c r="I3" t="n">
-        <v>23736000</v>
+        <v>-1648000</v>
       </c>
       <c r="J3" t="n">
-        <v>-359614000</v>
+        <v>-1539384000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1974973000</v>
+        <v>-2627539000</v>
       </c>
       <c r="L3" t="n">
-        <v>-326276000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>1217240000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-45274000</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-45274000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>-1636524000</v>
+        <v>-3766317000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1636524000</v>
+        <v>-3766317000</v>
       </c>
       <c r="S3" t="n">
-        <v>-2310166000</v>
+        <v>-5657270000</v>
       </c>
       <c r="T3" t="n">
-        <v>673642000</v>
+        <v>1890953000</v>
       </c>
       <c r="U3" t="n">
-        <v>270827000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>729639000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13954000</v>
+      </c>
       <c r="W3" t="n">
-        <v>17009000</v>
+        <v>292059000</v>
       </c>
       <c r="X3" t="n">
-        <v>12702000</v>
+        <v>14745000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-48578000</v>
+        <v>17579000</v>
       </c>
       <c r="Z3" t="n">
-        <v>37266000</v>
+        <v>35269000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-85844000</v>
+        <v>-17690000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-51000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>-5252000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-51000</v>
+        <v>-5252000</v>
       </c>
       <c r="AE3" t="n">
-        <v>49899000</v>
+        <v>227630000</v>
       </c>
       <c r="AF3" t="n">
-        <v>130659000</v>
+        <v>345560000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-80760000</v>
+        <v>-117930000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-25000</v>
+        <v>-1742000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25000</v>
+        <v>-1742000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2310000</v>
+        <v>-10177000</v>
       </c>
       <c r="AK3" t="n">
-        <v>214000</v>
+        <v>1186000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2524000</v>
+        <v>-11363000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1344532000</v>
+        <v>358516000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-87884000</v>
+        <v>-121631000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-325060000</v>
+        <v>-1005708000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1866735000</v>
+        <v>2101575000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2175455000</v>
+        <v>-1887757000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-572199000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-1809949000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
       <c r="AT3" t="n">
-        <v>4327286000</v>
+        <v>4501071000</v>
       </c>
       <c r="AU3" t="n">
-        <v>287103000</v>
+        <v>1298210000</v>
       </c>
       <c r="AV3" t="n">
-        <v>733684000</v>
+        <v>946169000</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>711000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>246566000</v>
+      </c>
       <c r="AY3" t="n">
-        <v>21174000</v>
+        <v>30385000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1385000</v>
+        <v>5115000</v>
       </c>
       <c r="BA3" t="n">
-        <v>19789000</v>
+        <v>25270000</v>
       </c>
       <c r="BB3" t="n">
-        <v>482053000</v>
+        <v>546269000</v>
       </c>
       <c r="BC3" t="n">
-        <v>164768000</v>
+        <v>883959000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-128000</v>
+        <v>-228000</v>
       </c>
       <c r="BE3" t="n">
-        <v>-16204000</v>
+        <v>328482000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1715512000</v>
+        <v>-4091441000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>345411000</v>
+        <v>1341983000</v>
       </c>
       <c r="C4" t="n">
-        <v>-5657270000</v>
+        <v>-2310166000</v>
       </c>
       <c r="D4" t="n">
-        <v>1890953000</v>
+        <v>673642000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-13105000</v>
+        <v>-2549000</v>
       </c>
       <c r="G4" t="n">
+        <v>334532000</v>
+      </c>
+      <c r="H4" t="n">
         <v>670410000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2211442000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-1648000</v>
+        <v>23736000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1539384000</v>
+        <v>-359614000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2627539000</v>
+        <v>-1974973000</v>
       </c>
       <c r="L4" t="n">
-        <v>1217240000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-45274000</v>
-      </c>
+        <v>-326276000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-45274000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-3766317000</v>
+        <v>-1636524000</v>
       </c>
       <c r="R4" t="n">
-        <v>-3766317000</v>
+        <v>-1636524000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5657270000</v>
+        <v>-2310166000</v>
       </c>
       <c r="T4" t="n">
-        <v>1890953000</v>
+        <v>673642000</v>
       </c>
       <c r="U4" t="n">
-        <v>729639000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>13954000</v>
-      </c>
+        <v>270827000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>292059000</v>
+        <v>17009000</v>
       </c>
       <c r="X4" t="n">
-        <v>14745000</v>
+        <v>12702000</v>
       </c>
       <c r="Y4" t="n">
-        <v>17579000</v>
+        <v>-48578000</v>
       </c>
       <c r="Z4" t="n">
-        <v>35269000</v>
+        <v>37266000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-17690000</v>
+        <v>-85844000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-5252000</v>
-      </c>
-      <c r="AC4" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>49899000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>130659000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-80760000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-2310000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>214000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-2524000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1344532000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-87884000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-325060000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1866735000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-2175455000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-572199000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>4327286000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>287103000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>733684000</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>-5252000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>227630000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>345560000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-117930000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1742000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1742000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-10177000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1186000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-11363000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>358516000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-121631000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-1005708000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2101575000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-1887757000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1809949000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4501071000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1298210000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>946169000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>711000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>246566000</v>
-      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>30385000</v>
+        <v>21174000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5115000</v>
+        <v>1385000</v>
       </c>
       <c r="BA4" t="n">
-        <v>25270000</v>
+        <v>19789000</v>
       </c>
       <c r="BB4" t="n">
-        <v>546269000</v>
+        <v>482053000</v>
       </c>
       <c r="BC4" t="n">
-        <v>883959000</v>
+        <v>164768000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-228000</v>
+        <v>-128000</v>
       </c>
       <c r="BE4" t="n">
-        <v>328482000</v>
+        <v>-16204000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-4091441000</v>
+        <v>-1715512000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-4853416000</v>
+        <v>38969000</v>
       </c>
       <c r="C5" t="n">
-        <v>-12344638000</v>
+        <v>-371109000</v>
       </c>
       <c r="D5" t="n">
-        <v>13406105000</v>
-      </c>
-      <c r="E5" t="n">
+        <v>99990000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>-7126000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>217757000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>334532000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-116760000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-288760000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-13567000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>-271119000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-271119000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-371109000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>99990000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>125905000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>1156000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13903000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>36569000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>36569000</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>-8748000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2211442000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10895964000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1385000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-8683137000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-3881587000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-4569424000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-350867000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-350867000</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1061467000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1061467000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-12344638000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>13406105000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>43118000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11195000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>328416000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>66280000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-168270000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>608736000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-777006000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>36374000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>45266000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-8892000</v>
-      </c>
       <c r="AE5" t="n">
-        <v>275443000</v>
+        <v>94012000</v>
       </c>
       <c r="AF5" t="n">
-        <v>340390000</v>
+        <v>94462000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-64947000</v>
+        <v>-450000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2854000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2854000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4122000</v>
+        <v>-7116000</v>
       </c>
       <c r="AK5" t="n">
-        <v>10016000</v>
+        <v>10000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-5894000</v>
+        <v>-7126000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-4844668000</v>
+        <v>46095000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-859109000</v>
+        <v>-32955000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1640806000</v>
+        <v>-104029000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3580567000</v>
+        <v>899891000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-7480018000</v>
+        <v>-3057696000</v>
       </c>
       <c r="AR5" t="n">
-        <v>733636000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1185476000</v>
-      </c>
+        <v>-1360194000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1127274000</v>
+        <v>4758809000</v>
       </c>
       <c r="AU5" t="n">
-        <v>853065000</v>
+        <v>558972000</v>
       </c>
       <c r="AV5" t="n">
-        <v>524544000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>837000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>71931000</v>
-      </c>
+        <v>722097000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>-16327000</v>
+        <v>12754000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1471000</v>
+        <v>153000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-17798000</v>
+        <v>12601000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-219291000</v>
+        <v>841004000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-254393000</v>
+        <v>149837000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-310000</v>
+        <v>4951000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-157645000</v>
+        <v>100923000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1040258000</v>
+        <v>-3334019000</v>
       </c>
     </row>
   </sheetData>
@@ -3923,192 +3923,192 @@
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Hao  Yan', 'age': 56, 'title': 'CEO &amp; Chairman of the Board', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 1597491, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Chen', 'age': 46, 'title': 'VP, CFO &amp; Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 1811802, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hai Feng  Xu', 'age': 51, 'title': 'VP &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2024, 'totalPay': 2228841, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bing Xian  Jiang', 'age': 44, 'title': 'Company Secretary &amp; General Legal Counsel', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Hao  Yan', 'age': 56, 'title': 'CEO &amp; Chairman of the Board', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 1596218, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Chen', 'age': 46, 'title': 'VP, CFO &amp; Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 1810358, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hai Feng  Xu', 'age': 51, 'title': 'VP &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2024, 'totalPay': 2227065, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bing Xian  Jiang', 'age': 44, 'title': 'Company Secretary &amp; General Legal Counsel', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4241,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="AF2" t="n">
         <v>34350000</v>
@@ -4295,7 +4295,7 @@
         <v>0.016</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.014805</v>
+        <v>0.014905</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>1538813213</v>
       </c>
       <c r="BI2" t="n">
-        <v>-3.6632025</v>
+        <v>-3.6612587</v>
       </c>
       <c r="BJ2" t="n">
         <v>1735603200</v>
@@ -4360,7 +4360,7 @@
         <v>0.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>0.25</v>
@@ -4472,141 +4472,141 @@
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="CX2" t="b">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>1768464488</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_247839378</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Jingrui Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>JINGRUI HLDGS</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
         <v>1383183000000</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DJ2" t="n">
         <v>0.0010000011</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>0.014 - 0.021</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="DM2" t="n">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DN2" t="n">
         <v>0.006000001</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DO2" t="n">
         <v>0.6000001</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>0.01 - 0.045</t>
         </is>
       </c>
-      <c r="DG2" t="n">
+      <c r="DQ2" t="n">
         <v>-0.029000001</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DR2" t="n">
         <v>-0.64444447</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DS2" t="n">
         <v>60.000004</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DT2" t="n">
         <v>1743172972</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>JINGRUI HLDGS</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Jingrui Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DU2" t="n">
         <v>1743172972</v>
       </c>
-      <c r="DN2" t="b">
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DW2" t="n">
         <v>-2.65</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DZ2" t="n">
         <v>0</v>
       </c>
-      <c r="DR2" t="n">
-        <v>0.0011950005</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.08071601</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.004367763</v>
-      </c>
-      <c r="DU2" t="n">
+      <c r="EA2" t="n">
+        <v>0.0010950007</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.073465325</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.004370082</v>
+      </c>
+      <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EE2" t="n">
         <v>15</v>
       </c>
-      <c r="DW2" t="b">
+      <c r="EF2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EG2" t="n">
         <v>6.6666746</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EH2" t="n">
         <v>0.016</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1768464488</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_247839378</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
